--- a/diseases/d123/1995-1999.xlsx
+++ b/diseases/d123/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>236</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>179</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>37</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>8</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>68</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>257</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>60</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>7</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20022,9 +19875,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20415,9 +20265,6 @@
       <c r="O102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20808,9 +20655,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21201,9 +21045,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21594,9 +21435,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21987,9 +21825,6 @@
       <c r="O110" t="n">
         <v>4</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22380,9 +22215,6 @@
       <c r="O112" t="n">
         <v>47</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22773,9 +22605,6 @@
       <c r="O114" t="n">
         <v>42</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23166,9 +22995,6 @@
       <c r="O116" t="n">
         <v>7</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23559,9 +23385,6 @@
       <c r="O118" t="n">
         <v>2</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23952,9 +23775,6 @@
       <c r="O120" t="n">
         <v>2</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24345,9 +24165,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24738,9 +24555,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25131,9 +24945,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25524,9 +25335,6 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25917,9 +25725,6 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26310,9 +26115,6 @@
       <c r="O132" t="n">
         <v>4</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26703,9 +26505,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27096,9 +26895,6 @@
       <c r="O136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27489,9 +27285,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27882,9 +27675,6 @@
       <c r="O140" t="n">
         <v>2</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28275,9 +28065,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28668,9 +28455,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29061,9 +28845,6 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29454,9 +29235,6 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29847,9 +29625,6 @@
       <c r="O150" t="n">
         <v>28</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30240,9 +30015,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30633,9 +30405,6 @@
       <c r="O154" t="n">
         <v>52</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31026,9 +30795,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31419,9 +31185,6 @@
       <c r="O158" t="n">
         <v>28</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31812,9 +31575,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32205,9 +31965,6 @@
       <c r="O162" t="n">
         <v>4</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32598,9 +32355,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32991,9 +32745,6 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33384,9 +33135,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33777,9 +33525,6 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34170,9 +33915,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34563,9 +34305,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34956,9 +34695,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35349,9 +35085,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35742,9 +35475,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36135,9 +35865,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36528,9 +36255,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36921,9 +36645,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37314,9 +37035,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37707,9 +37425,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38100,9 +37815,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38493,9 +38205,6 @@
       <c r="O194" t="n">
         <v>11</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38886,9 +38595,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39279,9 +38985,6 @@
       <c r="O198" t="n">
         <v>28</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39672,9 +39375,6 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40065,9 +39765,6 @@
       <c r="O202" t="n">
         <v>28</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40458,9 +40155,6 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40851,9 +40545,6 @@
       <c r="O206" t="n">
         <v>7</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41244,9 +40935,6 @@
       <c r="O208" t="n">
         <v>1</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41637,9 +41325,6 @@
       <c r="O210" t="n">
         <v>5</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42030,9 +41715,6 @@
       <c r="O212" t="n">
         <v>1</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42423,9 +42105,6 @@
       <c r="O214" t="n">
         <v>4</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42814,9 +42493,6 @@
         <v>0</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q216" t="n">
         <v>0</v>
       </c>
       <c r="S216" t="inlineStr">

--- a/diseases/d123/1995-1999.xlsx
+++ b/diseases/d123/1995-1999.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -795,17 +795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1021,7 +1026,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1029,17 +1034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1177,7 +1187,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1185,17 +1195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1411,7 +1426,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1419,17 +1434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1567,7 +1587,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1575,17 +1595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1801,7 +1826,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1809,17 +1834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1957,7 +1987,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2191,7 +2226,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2347,7 +2387,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2581,7 +2626,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2737,7 +2787,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2971,7 +3026,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3127,7 +3187,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3361,7 +3426,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3517,7 +3587,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3751,7 +3826,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3907,7 +3987,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4141,7 +4226,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4297,7 +4387,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4531,7 +4626,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4687,7 +4787,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4921,7 +5026,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +5034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5077,7 +5187,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5311,7 +5426,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5467,7 +5587,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5475,17 +5595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5701,7 +5826,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5709,17 +5834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5857,7 +5987,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5865,17 +5995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6091,7 +6226,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6099,17 +6234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6247,7 +6387,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6255,17 +6395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6481,7 +6626,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6489,17 +6634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6637,7 +6787,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6645,17 +6795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6871,7 +7026,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6879,17 +7034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -7027,7 +7187,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -7035,17 +7195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7261,7 +7426,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7269,17 +7434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7417,7 +7587,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7651,7 +7826,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7807,7 +7987,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7815,17 +7995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -8041,7 +8226,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8049,17 +8234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8197,7 +8387,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8431,7 +8626,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8587,7 +8787,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -8595,17 +8795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8821,7 +9026,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8829,17 +9034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8977,7 +9187,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8985,17 +9195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9211,7 +9426,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9367,7 +9587,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9375,17 +9595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9601,7 +9826,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9609,17 +9834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9757,7 +9987,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9765,17 +9995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9991,7 +10226,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,17 +10234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10147,7 +10387,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -10155,17 +10395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10381,7 +10626,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10389,17 +10634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10537,7 +10787,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10545,17 +10795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10771,7 +11026,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10779,17 +11034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10927,7 +11187,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -10935,17 +11195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11161,7 +11426,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -11169,17 +11434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11317,7 +11587,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11325,17 +11595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11551,7 +11826,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -11559,17 +11834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -11707,7 +11987,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -11715,17 +11995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -11941,7 +12226,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -11949,17 +12234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -12097,7 +12387,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12105,17 +12395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12331,7 +12626,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12339,17 +12634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12487,7 +12787,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12495,17 +12795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12721,7 +13026,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12729,17 +13034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12877,7 +13187,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12885,17 +13195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -13111,7 +13426,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13119,17 +13434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13267,7 +13587,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13275,17 +13595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13501,7 +13826,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13509,17 +13834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13657,7 +13987,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13665,17 +13995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13891,7 +14226,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13899,17 +14234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14047,7 +14387,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14055,17 +14395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14281,7 +14626,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14289,17 +14634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14437,7 +14787,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -14445,17 +14795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14671,7 +15026,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -14679,17 +15034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -14827,7 +15187,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -14835,17 +15195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS74" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -15061,7 +15426,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -15069,17 +15434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS75" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -15217,7 +15587,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -15225,17 +15595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -15451,7 +15826,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -15459,17 +15834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -15607,7 +15987,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -15615,17 +15995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -15841,7 +16226,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -15849,17 +16234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS79" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -15997,7 +16387,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -16005,17 +16395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -16231,7 +16626,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -16239,17 +16634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -16387,7 +16787,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -16395,17 +16795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS82" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -16621,7 +17026,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -16629,17 +17034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -16777,7 +17187,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -16785,17 +17195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -17011,7 +17426,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -17019,17 +17434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -17167,7 +17587,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -17175,17 +17595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS86" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -17401,7 +17826,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -17409,17 +17834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS87" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -17557,7 +17987,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -17565,17 +17995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -17791,7 +18226,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -17799,17 +18234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -17947,7 +18387,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -17955,17 +18395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -18181,7 +18626,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -18189,17 +18634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS91" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -18337,7 +18787,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -18345,17 +18795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS92" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -18571,7 +19026,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
@@ -18579,17 +19034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS93" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -18727,7 +19187,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -18735,17 +19195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS94" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -18961,7 +19426,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -18969,17 +19434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS95" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -19117,7 +19587,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -19125,17 +19595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -19351,7 +19826,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -19359,17 +19834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS97" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -19507,7 +19987,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -19515,17 +19995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS98" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -19741,7 +20226,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -19749,17 +20234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -19897,7 +20387,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
@@ -19905,17 +20395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS100" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -20131,7 +20626,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -20139,17 +20634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS101" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -20287,7 +20787,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -20295,17 +20795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS102" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -20521,7 +21026,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -20529,17 +21034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -20677,7 +21187,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -20685,17 +21195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -20911,7 +21426,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -20919,17 +21434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -21067,7 +21587,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -21075,17 +21595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -21301,7 +21826,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -21309,17 +21834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -21457,7 +21987,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -21465,17 +21995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -21691,7 +22226,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -21699,17 +22234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -21847,7 +22387,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -21855,17 +22395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -22081,7 +22626,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -22089,17 +22634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -22237,7 +22787,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
@@ -22245,17 +22795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS112" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -22471,7 +23026,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
@@ -22479,17 +23034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS113" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -22627,7 +23187,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
@@ -22635,17 +23195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS114" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -22861,7 +23426,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -22869,17 +23434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS115" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -23017,7 +23587,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -23025,17 +23595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -23251,7 +23826,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -23259,17 +23834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS117" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -23407,7 +23987,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
@@ -23415,17 +23995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS118" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -23641,7 +24226,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
@@ -23649,17 +24234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS119" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -23797,7 +24387,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -23805,17 +24395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -24031,7 +24626,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -24039,17 +24634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -24187,7 +24787,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -24195,17 +24795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS122" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -24421,7 +25026,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
@@ -24429,17 +25034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS123" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -24577,7 +25187,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
@@ -24585,17 +25195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS124" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -24811,7 +25426,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
@@ -24819,17 +25434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS125" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -24967,7 +25587,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
@@ -24975,17 +25595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS126" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -25201,7 +25826,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
@@ -25209,17 +25834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS127" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -25357,7 +25987,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
@@ -25365,17 +25995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS128" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -25591,7 +26226,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
@@ -25599,17 +26234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS129" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -25747,7 +26387,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
@@ -25755,17 +26395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS130" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -25981,7 +26626,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
@@ -25989,17 +26634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS131" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -26137,7 +26787,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
@@ -26145,17 +26795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS132" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -26371,7 +27026,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -26379,17 +27034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -26527,7 +27187,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -26535,17 +27195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -26761,7 +27426,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
@@ -26769,17 +27434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS135" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -26917,7 +27587,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -26925,17 +27595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS136" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -27151,7 +27826,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -27159,17 +27834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -27307,7 +27987,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -27315,17 +27995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -27541,7 +28226,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -27549,17 +28234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS139" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -27697,7 +28387,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
@@ -27705,17 +28395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS140" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -27931,7 +28626,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -27939,17 +28634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -28087,7 +28787,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
@@ -28095,17 +28795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS142" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -28321,7 +29026,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
@@ -28329,17 +29034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS143" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -28477,7 +29187,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
@@ -28485,17 +29195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS144" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -28711,7 +29426,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
@@ -28719,17 +29434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS145" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -28867,7 +29587,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
@@ -28875,17 +29595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS146" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -29101,7 +29826,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
@@ -29109,17 +29834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS147" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -29257,7 +29987,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
@@ -29265,17 +29995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS148" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -29491,7 +30226,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
@@ -29499,17 +30234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS149" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -29647,7 +30387,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
@@ -29655,17 +30395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS150" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -29881,7 +30626,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -29889,17 +30634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS151" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -30037,7 +30787,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -30045,17 +30795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS152" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -30271,7 +31026,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
@@ -30279,17 +31034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS153" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -30427,7 +31187,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
@@ -30435,17 +31195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS154" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -30661,7 +31426,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -30669,17 +31434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS155" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -30817,7 +31587,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -30825,17 +31595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS156" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -31051,7 +31826,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
@@ -31059,17 +31834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS157" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -31207,7 +31987,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
@@ -31215,17 +31995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS158" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -31441,7 +32226,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
@@ -31449,17 +32234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS159" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -31597,7 +32387,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
@@ -31605,17 +32395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS160" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -31831,7 +32626,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
@@ -31839,17 +32634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS161" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -31987,7 +32787,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
@@ -31995,17 +32795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS162" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -32221,7 +33026,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
@@ -32229,17 +33034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS163" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -32377,7 +33187,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
@@ -32385,17 +33195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS164" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -32611,7 +33426,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
@@ -32619,17 +33434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS165" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -32767,7 +33587,7 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
@@ -32775,17 +33595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS166" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -33001,7 +33826,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
@@ -33009,17 +33834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS167" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -33157,7 +33987,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
@@ -33165,17 +33995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS168" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -33391,7 +34226,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
@@ -33399,17 +34234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS169" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -33547,7 +34387,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
@@ -33555,17 +34395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS170" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -33781,7 +34626,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
@@ -33789,17 +34634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS171" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -33937,7 +34787,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
@@ -33945,17 +34795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS172" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -34171,7 +35026,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
@@ -34179,17 +35034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS173" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -34327,7 +35187,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
@@ -34335,17 +35195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS174" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -34561,7 +35426,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
@@ -34569,17 +35434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS175" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -34717,7 +35587,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -34725,17 +35595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS176" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -34951,7 +35826,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -34959,17 +35834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS177" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -35107,7 +35987,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
@@ -35115,17 +35995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS178" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -35341,7 +36226,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
@@ -35349,17 +36234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS179" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -35497,7 +36387,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
@@ -35505,17 +36395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS180" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -35731,7 +36626,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
@@ -35739,17 +36634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS181" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -35887,7 +36787,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
@@ -35895,17 +36795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS182" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -36121,7 +37026,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
@@ -36129,17 +37034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS183" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -36277,7 +37187,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
@@ -36285,17 +37195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS184" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -36511,7 +37426,7 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
@@ -36519,17 +37434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS185" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -36667,7 +37587,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
@@ -36675,17 +37595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS186" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -36901,7 +37826,7 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
@@ -36909,17 +37834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS187" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -37057,7 +37987,7 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ188" t="inlineStr">
@@ -37065,17 +37995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS188" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -37291,7 +38226,7 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
@@ -37299,17 +38234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS189" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -37447,7 +38387,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
@@ -37455,17 +38395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS190" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -37681,7 +38626,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
@@ -37689,17 +38634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS191" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -37837,7 +38787,7 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
@@ -37845,17 +38795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS192" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
@@ -38071,7 +39026,7 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
@@ -38079,17 +39034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS193" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
@@ -38227,7 +39187,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
@@ -38235,17 +39195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS194" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -38461,7 +39426,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
@@ -38469,17 +39434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS195" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -38617,7 +39587,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -38625,17 +39595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS196" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -38851,7 +39826,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -38859,17 +39834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS197" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -39007,7 +39987,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
@@ -39015,17 +39995,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS198" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
@@ -39241,7 +40226,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -39249,17 +40234,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS199" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -39397,7 +40387,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -39405,17 +40395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS200" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -39631,7 +40626,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -39639,17 +40634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -39787,7 +40787,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
@@ -39795,17 +40795,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS202" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -40021,7 +41026,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
@@ -40029,17 +41034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS203" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -40177,7 +41187,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -40185,17 +41195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS204" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -40411,7 +41426,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
@@ -40419,17 +41434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS205" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -40567,7 +41587,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
@@ -40575,17 +41595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS206" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -40801,7 +41826,7 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
@@ -40809,17 +41834,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS207" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -40957,7 +41987,7 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
@@ -40965,17 +41995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS208" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -41191,7 +42226,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
@@ -41199,17 +42234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS209" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -41347,7 +42387,7 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
@@ -41355,17 +42395,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS210" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -41581,7 +42626,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
@@ -41589,17 +42634,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS211" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -41737,7 +42787,7 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
@@ -41745,17 +42795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS212" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
@@ -41971,7 +43026,7 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ213" t="inlineStr">
@@ -41979,17 +43034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS213" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -42127,7 +43187,7 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ214" t="inlineStr">
@@ -42135,17 +43195,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS214" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -42361,7 +43426,7 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
@@ -42369,17 +43434,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS215" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1540</t>
         </is>
       </c>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -42517,7 +43587,7 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
@@ -42525,17 +43595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS216" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -42751,7 +43826,7 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
@@ -42759,17 +43834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS217" t="inlineStr">
         <is>
           <t>SER_NO_FHI_403_MONTHLY</t>
         </is>
       </c>
       <c r="AT217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
